--- a/Emmersive/package/LangMod/EN/emmersive_localizations.xlsx
+++ b/Emmersive/package/LangMod/EN/emmersive_localizations.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\WorkSpace\GameMods\Elin.Plugins\Emmersive\package\LangMod\EN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72EECEEA-8420-48FC-9A1F-19CCC4DEE64A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72D80CDA-776F-46E3-8D85-DC63B9576F42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8340" yWindow="2685" windowWidth="31695" windowHeight="18195" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="15375" yWindow="2685" windowWidth="31695" windowHeight="18195" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="General" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="432" uniqueCount="385">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="438" uniqueCount="391">
   <si>
     <t>id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -141,16 +141,16 @@
     <t>em_zone_data_name</t>
   </si>
   <si>
-    <t>em_zone_data_allow_crime</t>
+    <t>em_zone_data_crime</t>
   </si>
   <si>
     <t>em_zone_data_has_law</t>
   </si>
   <si>
-    <t>em_zone_data_is_town</t>
-  </si>
-  <si>
-    <t>em_zone_data_player_influence</t>
+    <t>em_zone_data_type</t>
+  </si>
+  <si>
+    <t>em_zone_data_influence</t>
   </si>
   <si>
     <t>em_character_data_name</t>
@@ -186,7 +186,7 @@
     <t>em_character_data_gender</t>
   </si>
   <si>
-    <t>em_character_data_background</t>
+    <t>em_character_data_persona</t>
   </si>
   <si>
     <t>em_character_data_fame</t>
@@ -225,7 +225,7 @@
     <t>em_player_data_gender</t>
   </si>
   <si>
-    <t>em_player_data_background</t>
+    <t>em_player_data_persona</t>
   </si>
   <si>
     <t>em_player_data_fame</t>
@@ -237,7 +237,7 @@
     <t>em_character_data_affinity</t>
   </si>
   <si>
-    <t>em_character_data_in_party</t>
+    <t>em_character_data_pc_party</t>
   </si>
   <si>
     <t>em_character_data_faith</t>
@@ -419,12 +419,6 @@
   <si>
     <t>APIキーを貼り付けてください
 ローカルのみで暗号化</t>
-  </si>
-  <si>
-    <t>しがいち</t>
-  </si>
-  <si>
-    <t>Town Area</t>
   </si>
   <si>
     <t>em_ui_open_sesame</t>
@@ -680,7 +674,7 @@
     <t>部屋の中で</t>
   </si>
   <si>
-    <t>em_character_data_conditions</t>
+    <t>em_character_data_condition</t>
   </si>
   <si>
     <t>em_ui_hard_reset_prompts</t>
@@ -1210,6 +1204,38 @@
   </si>
   <si>
     <t>記憶の要約をオン</t>
+  </si>
+  <si>
+    <t>エリア種別</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Zone Type</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>まだ短期記憶はありません</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>No short time memory yet.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>em_ui_no_stm</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>キャラクターを2人以上選択してください</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Select at least 2 characters</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>em_ui_relation_constraint</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1582,7 +1608,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:XFC144"/>
+  <dimension ref="A1:XFC146"/>
   <sheetFormatPr defaultColWidth="0" defaultRowHeight="23.25"/>
   <cols>
     <col min="1" max="1" width="63.28515625" style="4" customWidth="1"/>
@@ -1624,16 +1650,16 @@
     </row>
     <row r="4" spans="1:4" s="5" customFormat="1" ht="23.25" customHeight="1">
       <c r="A4" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="D4" s="4" t="s">
         <v>130</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>131</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>131</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>132</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1641,7 +1667,7 @@
         <v>5</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="D5" s="4" t="s">
         <v>8</v>
@@ -1652,10 +1678,10 @@
         <v>6</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1663,7 +1689,7 @@
         <v>7</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="D7" s="4" t="s">
         <v>9</v>
@@ -1674,7 +1700,7 @@
         <v>10</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="D8" s="4" t="s">
         <v>11</v>
@@ -1685,7 +1711,7 @@
         <v>12</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="D9" s="4" t="s">
         <v>13</v>
@@ -1696,7 +1722,7 @@
         <v>14</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D10" s="4" t="s">
         <v>15</v>
@@ -1707,7 +1733,7 @@
         <v>16</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="D11" s="4" t="s">
         <v>17</v>
@@ -1718,32 +1744,32 @@
         <v>18</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="4" t="s">
+        <v>326</v>
+      </c>
+      <c r="C13" s="4" t="s">
         <v>328</v>
       </c>
-      <c r="C13" s="4" t="s">
-        <v>330</v>
-      </c>
       <c r="D13" s="4" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="4" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -1751,10 +1777,10 @@
         <v>19</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -1796,10 +1822,10 @@
         <v>26</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="46.5">
@@ -1837,145 +1863,145 @@
     </row>
     <row r="23" spans="1:4">
       <c r="A23" s="4" t="s">
+        <v>211</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>212</v>
+      </c>
+      <c r="D23" s="4" t="s">
         <v>213</v>
-      </c>
-      <c r="C23" s="4" t="s">
-        <v>214</v>
-      </c>
-      <c r="D23" s="4" t="s">
-        <v>215</v>
       </c>
     </row>
     <row r="24" spans="1:4">
       <c r="A24" s="4" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
     </row>
     <row r="25" spans="1:4">
       <c r="A25" s="4" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="26" spans="1:4">
       <c r="A26" s="4" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
     </row>
     <row r="27" spans="1:4">
       <c r="A27" s="4" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="28" spans="1:4">
       <c r="A28" s="4" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="29" spans="1:4">
       <c r="A29" s="4" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="30" spans="1:4">
       <c r="A30" s="4" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
     </row>
     <row r="31" spans="1:4">
       <c r="A31" s="4" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
     </row>
     <row r="32" spans="1:4">
       <c r="A32" s="4" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
     <row r="33" spans="1:4">
       <c r="A33" s="4" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
     </row>
     <row r="34" spans="1:4">
       <c r="A34" s="4" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
     </row>
     <row r="35" spans="1:4" ht="69.75">
       <c r="A35" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="C35" s="4" t="s">
         <v>164</v>
       </c>
-      <c r="C35" s="4" t="s">
-        <v>166</v>
-      </c>
       <c r="D35" s="4" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2050,10 +2076,10 @@
         <v>37</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>128</v>
+        <v>383</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>129</v>
+        <v>384</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2412,161 +2438,161 @@
     </row>
     <row r="75" spans="1:4">
       <c r="A75" s="4" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C75" s="4" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="D75" s="4" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
     </row>
     <row r="76" spans="1:4">
       <c r="A76" s="4" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C76" s="4" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="D76" s="4" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="77" spans="1:4">
       <c r="A77" s="4" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="C77" s="4" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="D77" s="4" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="78" spans="1:4" ht="46.5">
       <c r="A78" s="4" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="C78" s="4" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="D78" s="4" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="79" spans="1:4" ht="46.5">
       <c r="A79" s="4" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="C79" s="4" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="D79" s="4" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="80" spans="1:4">
       <c r="A80" s="4" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="C80" s="4" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="D80" s="4" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="81" spans="1:4" ht="46.5">
       <c r="A81" s="4" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C81" s="4" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="D81" s="4" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
     </row>
     <row r="82" spans="1:4">
       <c r="A82" s="4" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C82" s="4" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D82" s="4" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="83" spans="1:4">
       <c r="A83" s="4" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="C83" s="4" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D83" s="4" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="84" spans="1:4">
       <c r="A84" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="C84" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="D84" s="4" t="s">
         <v>190</v>
-      </c>
-      <c r="C84" s="4" t="s">
-        <v>191</v>
-      </c>
-      <c r="D84" s="4" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="85" spans="1:4">
       <c r="A85" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="C85" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="D85" s="4" t="s">
         <v>196</v>
-      </c>
-      <c r="C85" s="4" t="s">
-        <v>195</v>
-      </c>
-      <c r="D85" s="4" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="86" spans="1:4">
       <c r="A86" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="C86" s="4" t="s">
         <v>197</v>
       </c>
-      <c r="C86" s="4" t="s">
-        <v>199</v>
-      </c>
       <c r="D86" s="4" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
     </row>
     <row r="87" spans="1:4">
       <c r="A87" s="4" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="C87" s="4" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="D87" s="4" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
     </row>
     <row r="88" spans="1:4">
       <c r="A88" s="4" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C88" s="4" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="D88" s="4" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
     </row>
     <row r="89" spans="1:4">
       <c r="A89" s="4" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="C89" s="4" t="s">
         <v>120</v>
@@ -2577,607 +2603,629 @@
     </row>
     <row r="90" spans="1:4">
       <c r="A90" s="4" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C90" s="4" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="D90" s="4" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
     </row>
     <row r="91" spans="1:4">
       <c r="A91" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C91" s="4" t="s">
+        <v>208</v>
+      </c>
+      <c r="D91" s="4" t="s">
         <v>206</v>
-      </c>
-      <c r="C91" s="4" t="s">
-        <v>210</v>
-      </c>
-      <c r="D91" s="4" t="s">
-        <v>208</v>
       </c>
     </row>
     <row r="92" spans="1:4">
       <c r="A92" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="C92" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="D92" s="4" t="s">
         <v>207</v>
-      </c>
-      <c r="C92" s="4" t="s">
-        <v>211</v>
-      </c>
-      <c r="D92" s="4" t="s">
-        <v>209</v>
       </c>
     </row>
     <row r="93" spans="1:4">
       <c r="A93" s="4" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="C93" s="4" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D93" s="4" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
     <row r="94" spans="1:4">
       <c r="A94" s="4" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="C94" s="4" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="D94" s="4" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
     </row>
     <row r="95" spans="1:4">
       <c r="A95" s="4" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C95" s="4" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="D95" s="4" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
     </row>
     <row r="96" spans="1:4">
       <c r="A96" s="4" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="C96" s="4" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="D96" s="4" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
     </row>
     <row r="97" spans="1:4">
       <c r="A97" s="4" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="C97" s="4" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="D97" s="4" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
     </row>
     <row r="98" spans="1:4">
       <c r="A98" s="4" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="C98" s="4" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="D98" s="4" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
     </row>
     <row r="99" spans="1:4">
       <c r="A99" s="4" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C99" s="4" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="D99" s="4" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
     </row>
     <row r="100" spans="1:4">
       <c r="A100" s="4" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C100" s="4" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="D100" s="4" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="101" spans="1:4">
       <c r="A101" s="4" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C101" s="4" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D101" s="4" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
     </row>
     <row r="102" spans="1:4">
       <c r="A102" s="4" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C102" s="4" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="D102" s="4" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
     </row>
     <row r="103" spans="1:4">
       <c r="A103" s="4" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="C103" s="4" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="D103" s="4" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
     </row>
     <row r="104" spans="1:4">
       <c r="A104" s="4" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="C104" s="4" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="D104" s="4" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
     </row>
     <row r="105" spans="1:4">
       <c r="A105" s="4" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="C105" s="4" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="D105" s="4" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="106" spans="1:4">
       <c r="A106" s="4" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="C106" s="4" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="D106" s="4" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
     </row>
     <row r="107" spans="1:4">
       <c r="A107" s="4" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="C107" s="4" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="D107" s="4" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
     </row>
     <row r="108" spans="1:4">
       <c r="A108" s="4" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C108" s="4" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="D108" s="4" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
     </row>
     <row r="109" spans="1:4">
       <c r="A109" s="4" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="C109" s="4" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="D109" s="4" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
     </row>
     <row r="110" spans="1:4">
       <c r="A110" s="4" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="C110" s="4" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="D110" s="4" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
     </row>
     <row r="111" spans="1:4">
       <c r="A111" s="4" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="C111" s="4" t="s">
+        <v>265</v>
+      </c>
+      <c r="D111" s="4" t="s">
         <v>267</v>
-      </c>
-      <c r="D111" s="4" t="s">
-        <v>269</v>
       </c>
     </row>
     <row r="112" spans="1:4">
       <c r="A112" s="4" t="s">
+        <v>268</v>
+      </c>
+      <c r="C112" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="D112" s="4" t="s">
         <v>270</v>
-      </c>
-      <c r="C112" s="4" t="s">
-        <v>271</v>
-      </c>
-      <c r="D112" s="4" t="s">
-        <v>272</v>
       </c>
     </row>
     <row r="113" spans="1:4">
       <c r="A113" s="4" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="C113" s="4" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="D113" s="4" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
     </row>
     <row r="114" spans="1:4">
       <c r="A114" s="4" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="C114" s="4" t="s">
+        <v>276</v>
+      </c>
+      <c r="D114" s="4" t="s">
         <v>278</v>
-      </c>
-      <c r="D114" s="4" t="s">
-        <v>280</v>
       </c>
     </row>
     <row r="115" spans="1:4">
       <c r="A115" s="4" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="C115" s="4" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="D115" s="4" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
     </row>
     <row r="116" spans="1:4">
       <c r="A116" s="4" t="s">
+        <v>281</v>
+      </c>
+      <c r="C116" s="4" t="s">
         <v>283</v>
       </c>
-      <c r="C116" s="4" t="s">
-        <v>285</v>
-      </c>
       <c r="D116" s="4" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
     </row>
     <row r="117" spans="1:4">
       <c r="A117" s="4" t="s">
+        <v>284</v>
+      </c>
+      <c r="C117" s="4" t="s">
         <v>286</v>
       </c>
-      <c r="C117" s="4" t="s">
-        <v>288</v>
-      </c>
       <c r="D117" s="4" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
     </row>
     <row r="118" spans="1:4">
       <c r="A118" s="4" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="C118" s="4" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="D118" s="4" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="119" spans="1:4">
       <c r="A119" s="4" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="C119" s="4" t="s">
+        <v>290</v>
+      </c>
+      <c r="D119" s="4" t="s">
         <v>292</v>
-      </c>
-      <c r="D119" s="4" t="s">
-        <v>294</v>
       </c>
     </row>
     <row r="120" spans="1:4">
       <c r="A120" s="4" t="s">
+        <v>293</v>
+      </c>
+      <c r="C120" s="4" t="s">
         <v>295</v>
       </c>
-      <c r="C120" s="4" t="s">
-        <v>297</v>
-      </c>
       <c r="D120" s="4" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
     </row>
     <row r="121" spans="1:4">
       <c r="A121" s="4" t="s">
+        <v>296</v>
+      </c>
+      <c r="C121" s="6" t="s">
+        <v>297</v>
+      </c>
+      <c r="D121" s="4" t="s">
         <v>298</v>
-      </c>
-      <c r="C121" s="6" t="s">
-        <v>299</v>
-      </c>
-      <c r="D121" s="4" t="s">
-        <v>300</v>
       </c>
     </row>
     <row r="122" spans="1:4">
       <c r="A122" s="4" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="C122" s="4" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="D122" s="4" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
     </row>
     <row r="123" spans="1:4">
       <c r="A123" s="4" t="s">
+        <v>300</v>
+      </c>
+      <c r="C123" s="4" t="s">
         <v>302</v>
       </c>
-      <c r="C123" s="4" t="s">
-        <v>304</v>
-      </c>
       <c r="D123" s="4" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
     </row>
     <row r="124" spans="1:4">
       <c r="A124" s="4" t="s">
+        <v>306</v>
+      </c>
+      <c r="C124" s="4" t="s">
+        <v>307</v>
+      </c>
+      <c r="D124" s="4" t="s">
         <v>308</v>
-      </c>
-      <c r="C124" s="4" t="s">
-        <v>309</v>
-      </c>
-      <c r="D124" s="4" t="s">
-        <v>310</v>
       </c>
     </row>
     <row r="125" spans="1:4">
       <c r="A125" s="4" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="C125" s="4" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="D125" s="4" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
     </row>
     <row r="126" spans="1:4" ht="139.5">
       <c r="A126" s="4" t="s">
+        <v>310</v>
+      </c>
+      <c r="C126" s="4" t="s">
+        <v>311</v>
+      </c>
+      <c r="D126" s="7" t="s">
         <v>312</v>
-      </c>
-      <c r="C126" s="4" t="s">
-        <v>313</v>
-      </c>
-      <c r="D126" s="7" t="s">
-        <v>314</v>
       </c>
     </row>
     <row r="127" spans="1:4" ht="69.75">
       <c r="A127" s="4" t="s">
+        <v>314</v>
+      </c>
+      <c r="C127" s="4" t="s">
         <v>316</v>
       </c>
-      <c r="C127" s="4" t="s">
-        <v>318</v>
-      </c>
       <c r="D127" s="4" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
     </row>
     <row r="128" spans="1:4">
       <c r="A128" s="4" t="s">
+        <v>317</v>
+      </c>
+      <c r="C128" s="4" t="s">
         <v>319</v>
       </c>
-      <c r="C128" s="4" t="s">
-        <v>321</v>
-      </c>
       <c r="D128" s="4" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
     </row>
     <row r="129" spans="1:4">
       <c r="A129" s="4" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="C129" s="4" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="D129" s="4" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
     </row>
     <row r="130" spans="1:4" ht="46.5">
       <c r="A130" s="4" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="C130" s="4" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="D130" s="4" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
     </row>
     <row r="131" spans="1:4">
       <c r="A131" s="4" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="C131" s="8" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="D131" s="4" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
     </row>
     <row r="132" spans="1:4">
       <c r="A132" s="4" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="C132" s="8" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="D132" s="4" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
     </row>
     <row r="133" spans="1:4">
       <c r="A133" s="4" t="s">
+        <v>343</v>
+      </c>
+      <c r="C133" s="8" t="s">
         <v>345</v>
       </c>
-      <c r="C133" s="8" t="s">
-        <v>347</v>
-      </c>
       <c r="D133" s="4" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
     </row>
     <row r="134" spans="1:4">
       <c r="A134" s="4" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="C134" s="4" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="D134" s="4" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
     </row>
     <row r="135" spans="1:4">
       <c r="A135" s="4" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="C135" s="4" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="D135" s="4" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
     </row>
     <row r="136" spans="1:4">
       <c r="A136" s="4" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="C136" s="4" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="D136" s="4" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
     </row>
     <row r="137" spans="1:4">
       <c r="A137" s="4" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="C137" s="4" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="D137" s="4" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
     </row>
     <row r="138" spans="1:4">
       <c r="A138" s="4" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="C138" s="4" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="D138" s="4" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
     </row>
     <row r="139" spans="1:4">
       <c r="A139" s="4" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="C139" s="4" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="D139" s="4" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
     </row>
     <row r="140" spans="1:4">
       <c r="A140" s="4" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="C140" s="4" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="D140" s="4" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
     </row>
     <row r="141" spans="1:4">
       <c r="A141" s="4" t="s">
+        <v>371</v>
+      </c>
+      <c r="C141" s="4" t="s">
         <v>373</v>
       </c>
-      <c r="C141" s="4" t="s">
-        <v>375</v>
-      </c>
       <c r="D141" s="4" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
     </row>
     <row r="142" spans="1:4">
       <c r="A142" s="4" t="s">
+        <v>374</v>
+      </c>
+      <c r="C142" s="4" t="s">
         <v>376</v>
       </c>
-      <c r="C142" s="4" t="s">
-        <v>378</v>
-      </c>
       <c r="D142" s="4" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
     </row>
     <row r="143" spans="1:4">
       <c r="A143" s="4" t="s">
+        <v>377</v>
+      </c>
+      <c r="C143" s="4" t="s">
         <v>379</v>
       </c>
-      <c r="C143" s="4" t="s">
-        <v>381</v>
-      </c>
       <c r="D143" s="4" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
     </row>
     <row r="144" spans="1:4">
       <c r="A144" s="4" t="s">
+        <v>380</v>
+      </c>
+      <c r="C144" s="4" t="s">
         <v>382</v>
       </c>
-      <c r="C144" s="4" t="s">
-        <v>384</v>
-      </c>
       <c r="D144" s="4" t="s">
-        <v>383</v>
+        <v>381</v>
+      </c>
+    </row>
+    <row r="145" spans="1:4">
+      <c r="A145" s="4" t="s">
+        <v>387</v>
+      </c>
+      <c r="C145" s="4" t="s">
+        <v>385</v>
+      </c>
+      <c r="D145" s="4" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="146" spans="1:4">
+      <c r="A146" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="C146" s="4" t="s">
+        <v>388</v>
+      </c>
+      <c r="D146" s="4" t="s">
+        <v>389</v>
       </c>
     </row>
   </sheetData>

--- a/Emmersive/package/LangMod/EN/emmersive_localizations.xlsx
+++ b/Emmersive/package/LangMod/EN/emmersive_localizations.xlsx
@@ -2569,12 +2569,12 @@
       </c>
       <c r="C124" s="4" t="inlineStr">
         <is>
-          <t>要約が完了し、長期記憶を{0}件追加しました</t>
+          <t>要約が完了し、長期記憶を{0}件追加・更新しました</t>
         </is>
       </c>
       <c r="D124" s="4" t="inlineStr">
         <is>
-          <t>Summary done: {0} new fact(s) added</t>
+          <t>Summary done: {0} fact(s) added or updated</t>
         </is>
       </c>
     </row>
